--- a/Data Final/Final_PM15-1.xlsx
+++ b/Data Final/Final_PM15-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kuliah\Sun Paper Source\Y Prediction\Data Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1AAD91-8BC2-4F66-9354-A465EC8CF413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B50AA4B-196B-4B38-8DDD-FF86F0BAB6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1464" yWindow="1464" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1148,7 +1148,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -1181,7 +1181,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1488,17 +1488,17 @@
   <dimension ref="A1:AM441"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="0" hidden="1" customWidth="1"/>
+    <col min="1" max="3" width="8.88671875" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.109375" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="20.33203125" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="20.109375" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="15.5546875" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="21.5546875" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.44140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5546875" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="28.33203125" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="22.5546875" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="18.33203125" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="18.109375" hidden="1" customWidth="1"/>
@@ -1509,11 +1509,10 @@
     <col min="21" max="21" width="4.5546875" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="6" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="8.77734375" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5" hidden="1" customWidth="1"/>
+    <col min="24" max="25" width="5" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="6.6640625" hidden="1" customWidth="1"/>
     <col min="27" max="27" width="24.44140625" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="4.77734375" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="4.77734375" customWidth="1"/>
     <col min="29" max="29" width="9.33203125" hidden="1" customWidth="1"/>
     <col min="30" max="30" width="10.33203125" hidden="1" customWidth="1"/>
     <col min="31" max="31" width="5" customWidth="1"/>
@@ -1521,7 +1520,7 @@
     <col min="33" max="33" width="9.6640625" hidden="1" customWidth="1"/>
     <col min="34" max="34" width="14.6640625" hidden="1" customWidth="1"/>
     <col min="35" max="35" width="18.44140625" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="12" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12" hidden="1" customWidth="1"/>
     <col min="37" max="37" width="6.88671875" hidden="1" customWidth="1"/>
     <col min="38" max="38" width="12" hidden="1" customWidth="1"/>
     <col min="39" max="39" width="12.109375" hidden="1" customWidth="1"/>
@@ -3193,7 +3192,7 @@
         <v>802695.52850849961</v>
       </c>
     </row>
-    <row r="15" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46099.28125</v>
       </c>
@@ -3312,7 +3311,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="16" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46100.295138888891</v>
       </c>
@@ -3431,7 +3430,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="17" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46100.371527777781</v>
       </c>
@@ -3550,7 +3549,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="18" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46100.40625</v>
       </c>
@@ -3669,7 +3668,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="19" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46100.447916666657</v>
       </c>
@@ -3788,7 +3787,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="20" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46100.489583333343</v>
       </c>
@@ -3907,7 +3906,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="21" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46100.503472222219</v>
       </c>
@@ -4026,7 +4025,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="22" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46100.545138888891</v>
       </c>
@@ -4145,7 +4144,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="23" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46100.586805555547</v>
       </c>
@@ -4264,7 +4263,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="24" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46100.663194444453</v>
       </c>
@@ -4383,7 +4382,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="25" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46100.670138888891</v>
       </c>
@@ -4502,7 +4501,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="26" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46100.711805555547</v>
       </c>
@@ -4621,7 +4620,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="27" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46100.75277777778</v>
       </c>
@@ -4740,7 +4739,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="28" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46100.794444444437</v>
       </c>
@@ -4859,7 +4858,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="29" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46100.857638888891</v>
       </c>
@@ -4978,7 +4977,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="30" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46100.87777777778</v>
       </c>
@@ -5097,7 +5096,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="31" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46100.918055555558</v>
       </c>
@@ -5216,7 +5215,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="32" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46100.969444444447</v>
       </c>
@@ -5335,7 +5334,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="33" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46100.009722222218</v>
       </c>
@@ -5454,7 +5453,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="34" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46100.053472222222</v>
       </c>
@@ -5573,7 +5572,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="35" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46100.086805555547</v>
       </c>
@@ -5692,7 +5691,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="36" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46100.167361111111</v>
       </c>
@@ -5811,7 +5810,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="37" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46100.167361111111</v>
       </c>
@@ -5930,7 +5929,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="38" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46100.211805555547</v>
       </c>
@@ -6049,7 +6048,7 @@
         <v>894024.67850849964</v>
       </c>
     </row>
-    <row r="39" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46100.27847222222</v>
       </c>
@@ -6168,7 +6167,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="40" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46101.322916666657</v>
       </c>
@@ -6287,7 +6286,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="41" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46101.371527777781</v>
       </c>
@@ -6406,7 +6405,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="42" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46101.416666666657</v>
       </c>
@@ -6525,7 +6524,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="43" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46101.458333333343</v>
       </c>
@@ -6644,7 +6643,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="44" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46101.5</v>
       </c>
@@ -6763,7 +6762,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="45" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46101.541666666657</v>
       </c>
@@ -6882,7 +6881,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="46" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46101.583333333343</v>
       </c>
@@ -7001,7 +7000,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="47" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46101.626388888893</v>
       </c>
@@ -7120,7 +7119,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="48" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46101.668055555558</v>
       </c>
@@ -7239,7 +7238,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="49" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46101.725694444453</v>
       </c>
@@ -7358,7 +7357,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="50" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46101.752083333333</v>
       </c>
@@ -7477,7 +7476,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="51" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46101.820833333331</v>
       </c>
@@ -7596,7 +7595,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="52" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46101.862500000003</v>
       </c>
@@ -7715,7 +7714,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="53" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46101.87777777778</v>
       </c>
@@ -7834,7 +7833,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="54" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46101.938194444447</v>
       </c>
@@ -7953,7 +7952,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="55" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46101.981944444437</v>
       </c>
@@ -8072,7 +8071,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="56" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46101.002083333333</v>
       </c>
@@ -8191,7 +8190,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="57" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46101.065972222219</v>
       </c>
@@ -8310,7 +8309,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="58" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46101.09375</v>
       </c>
@@ -8429,7 +8428,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="59" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46101.138194444437</v>
       </c>
@@ -8548,7 +8547,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="60" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46101.177777777782</v>
       </c>
@@ -8667,7 +8666,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="61" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>46101.209027777782</v>
       </c>
@@ -8786,7 +8785,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="62" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46101.23333333333</v>
       </c>
@@ -8905,7 +8904,7 @@
         <v>942499.40954778471</v>
       </c>
     </row>
-    <row r="63" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46101.274305555547</v>
       </c>
@@ -9024,7 +9023,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="64" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46102.294444444437</v>
       </c>
@@ -9143,7 +9142,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="65" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46102.336111111108</v>
       </c>
@@ -9262,7 +9261,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="66" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46102.37777777778</v>
       </c>
@@ -9381,7 +9380,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="67" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46102.447916666657</v>
       </c>
@@ -9500,7 +9499,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="68" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46102.489583333343</v>
       </c>
@@ -9619,7 +9618,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="69" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46102.53125</v>
       </c>
@@ -9738,7 +9737,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="70" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46102.572916666657</v>
       </c>
@@ -9857,7 +9856,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="71" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>46102.614583333343</v>
       </c>
@@ -9976,7 +9975,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="72" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46102.65625</v>
       </c>
@@ -10095,7 +10094,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="73" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>46102.697916666657</v>
       </c>
@@ -10214,7 +10213,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="74" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46102.732638888891</v>
       </c>
@@ -10333,7 +10332,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="75" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46102.75277777778</v>
       </c>
@@ -10452,7 +10451,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="76" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46102.793749999997</v>
       </c>
@@ -10571,7 +10570,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="77" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46102.834722222222</v>
       </c>
@@ -10690,7 +10689,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="78" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>46102.875</v>
       </c>
@@ -10809,7 +10808,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="79" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>46102.918749999997</v>
       </c>
@@ -10928,7 +10927,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="80" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>46102.960416666669</v>
       </c>
@@ -11047,7 +11046,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="81" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>46102.011111111111</v>
       </c>
@@ -11166,7 +11165,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="82" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46102.056250000001</v>
       </c>
@@ -11285,7 +11284,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="83" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>46102.09652777778</v>
       </c>
@@ -11404,7 +11403,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="84" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46102.140277777777</v>
       </c>
@@ -11523,7 +11522,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="85" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46102.177777777782</v>
       </c>
@@ -11642,7 +11641,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="86" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>46102.21597222222</v>
       </c>
@@ -11761,7 +11760,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="87" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>46102.248611111107</v>
       </c>
@@ -11880,7 +11879,7 @@
         <v>992925.66216581129</v>
       </c>
     </row>
-    <row r="88" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>46105.25277777778</v>
       </c>
@@ -11999,7 +11998,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="89" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>46106.320138888892</v>
       </c>
@@ -12118,7 +12117,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="90" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>46106.334722222222</v>
       </c>
@@ -12237,7 +12236,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="91" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>46106.401388888888</v>
       </c>
@@ -12356,7 +12355,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="92" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>46106.446527777778</v>
       </c>
@@ -12475,7 +12474,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="93" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>46106.488888888889</v>
       </c>
@@ -12594,7 +12593,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="94" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>46106.503472222219</v>
       </c>
@@ -12713,7 +12712,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="95" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>46106.558333333327</v>
       </c>
@@ -12832,7 +12831,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="96" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>46106.585416666669</v>
       </c>
@@ -12951,7 +12950,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="97" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>46106.643055555563</v>
       </c>
@@ -13070,7 +13069,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="98" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>46106.678472222222</v>
       </c>
@@ -13189,7 +13188,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="99" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>46106.719444444447</v>
       </c>
@@ -13308,7 +13307,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="100" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>46106.761111111111</v>
       </c>
@@ -13427,7 +13426,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="101" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>46106.801388888889</v>
       </c>
@@ -13546,7 +13545,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="102" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>46106.845833333333</v>
       </c>
@@ -13665,7 +13664,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="103" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>46106.887499999997</v>
       </c>
@@ -13784,7 +13783,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="104" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>46106.928472222222</v>
       </c>
@@ -13903,7 +13902,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="105" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>46106.959722222222</v>
       </c>
@@ -14022,7 +14021,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="106" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>46106.010416666657</v>
       </c>
@@ -14141,7 +14140,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="107" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>46106.052083333343</v>
       </c>
@@ -14260,7 +14259,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="108" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>46106.084027777782</v>
       </c>
@@ -14379,7 +14378,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="109" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>46106.128472222219</v>
       </c>
@@ -14498,7 +14497,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="110" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>46106.170138888891</v>
       </c>
@@ -14617,7 +14616,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="111" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>46106.211111111108</v>
       </c>
@@ -14736,7 +14735,7 @@
         <v>1209824.8701153949</v>
       </c>
     </row>
-    <row r="112" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>46106.274305555547</v>
       </c>
@@ -14855,7 +14854,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="113" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>46107.316666666673</v>
       </c>
@@ -14974,7 +14973,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="114" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>46107.364583333343</v>
       </c>
@@ -15093,7 +15092,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="115" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>46107.40347222222</v>
       </c>
@@ -15212,7 +15211,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="116" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>46107.447916666657</v>
       </c>
@@ -15331,7 +15330,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="117" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>46107.461805555547</v>
       </c>
@@ -15450,7 +15449,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="118" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>46107.529861111107</v>
       </c>
@@ -15569,7 +15568,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="119" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>46107.543749999997</v>
       </c>
@@ -15688,7 +15687,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="120" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>46107.60833333333</v>
       </c>
@@ -15807,7 +15806,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="121" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>46107.647222222222</v>
       </c>
@@ -15926,7 +15925,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="122" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>46107.696527777778</v>
       </c>
@@ -16045,7 +16044,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="123" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>46107.732638888891</v>
       </c>
@@ -16164,7 +16163,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="124" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>46107.759027777778</v>
       </c>
@@ -16283,7 +16282,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="125" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>46107.795138888891</v>
       </c>
@@ -16402,7 +16401,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="126" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>46107.829861111109</v>
       </c>
@@ -16521,7 +16520,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="127" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>46107.863888888889</v>
       </c>
@@ -16640,7 +16639,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="128" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>46107.899305555547</v>
       </c>
@@ -16759,7 +16758,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="129" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>46107.931944444441</v>
       </c>
@@ -16878,7 +16877,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="130" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>46107.959722222222</v>
       </c>
@@ -16997,7 +16996,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="131" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>46107.024305555547</v>
       </c>
@@ -17116,7 +17115,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="132" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>46107.044444444437</v>
       </c>
@@ -17235,7 +17234,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="133" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>46107.086111111108</v>
       </c>
@@ -17354,7 +17353,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="134" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>46107.149305555547</v>
       </c>
@@ -17473,7 +17472,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="135" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>46107.168749999997</v>
       </c>
@@ -17592,7 +17591,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="136" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>46107.225694444453</v>
       </c>
@@ -17711,7 +17710,7 @@
         <v>1267623.6979501969</v>
       </c>
     </row>
-    <row r="137" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>46109.252083333333</v>
       </c>
@@ -17830,7 +17829,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="138" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>46110.313194444447</v>
       </c>
@@ -17949,7 +17948,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="139" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>46110.351388888892</v>
       </c>
@@ -18068,7 +18067,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="140" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>46110.406944444447</v>
       </c>
@@ -18187,7 +18186,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="141" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>46110.441666666673</v>
       </c>
@@ -18306,7 +18305,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="142" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>46110.460416666669</v>
       </c>
@@ -18425,7 +18424,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="143" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>46110.501388888893</v>
       </c>
@@ -18544,7 +18543,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="144" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>46110.501388888893</v>
       </c>
@@ -18663,7 +18662,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="145" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>46110.545138888891</v>
       </c>
@@ -18782,7 +18781,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="146" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>46110.611805555563</v>
       </c>
@@ -18901,7 +18900,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="147" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>46110.652083333327</v>
       </c>
@@ -19020,7 +19019,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="148" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>46110.69027777778</v>
       </c>
@@ -19139,7 +19138,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="149" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>46110.734722222223</v>
       </c>
@@ -19258,7 +19257,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="150" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>46110.768750000003</v>
       </c>
@@ -19377,7 +19376,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="151" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>46110.793055555558</v>
       </c>
@@ -19496,7 +19495,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="152" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>46110.859027777777</v>
       </c>
@@ -19615,7 +19614,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="153" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>46110.893055555563</v>
       </c>
@@ -19734,7 +19733,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="154" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>46110.931250000001</v>
       </c>
@@ -19853,7 +19852,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="155" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>46110.96875</v>
       </c>
@@ -19972,7 +19971,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="156" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>46110.003472222219</v>
       </c>
@@ -20091,7 +20090,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="157" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>46110.038194444453</v>
       </c>
@@ -20210,7 +20209,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="158" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>46110.045138888891</v>
       </c>
@@ -20329,7 +20328,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="159" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>46110.086111111108</v>
       </c>
@@ -20448,7 +20447,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="160" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>46110.149305555547</v>
       </c>
@@ -20567,7 +20566,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="161" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>46110.184027777781</v>
       </c>
@@ -20686,7 +20685,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="162" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>46110.21875</v>
       </c>
@@ -20805,7 +20804,7 @@
         <v>1448582.28880323</v>
       </c>
     </row>
-    <row r="163" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>46110.250694444447</v>
       </c>
@@ -20924,7 +20923,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="164" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>46111.295138888891</v>
       </c>
@@ -21043,7 +21042,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="165" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>46111.29583333333</v>
       </c>
@@ -21162,7 +21161,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="166" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>46111.336111111108</v>
       </c>
@@ -21281,7 +21280,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="167" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>46111.42083333333</v>
       </c>
@@ -21400,7 +21399,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="168" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>46111.456944444442</v>
       </c>
@@ -21519,7 +21518,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="169" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>46111.481249999997</v>
       </c>
@@ -21638,7 +21637,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="170" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>46111.512499999997</v>
       </c>
@@ -21757,7 +21756,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="171" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>46111.543749999997</v>
       </c>
@@ -21876,7 +21875,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="172" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>46111.601388888892</v>
       </c>
@@ -21995,7 +21994,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="173" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>46111.626388888893</v>
       </c>
@@ -22114,7 +22113,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="174" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>46111.679166666669</v>
       </c>
@@ -22233,7 +22232,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="175" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>46111.716666666667</v>
       </c>
@@ -22352,7 +22351,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="176" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>46111.750694444447</v>
       </c>
@@ -22471,7 +22470,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="177" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>46111.801388888889</v>
       </c>
@@ -22590,7 +22589,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="178" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>46111.85833333333</v>
       </c>
@@ -22709,7 +22708,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="179" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>46111.918055555558</v>
       </c>
@@ -22828,7 +22827,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="180" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>46111.975694444453</v>
       </c>
@@ -22947,7 +22946,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="181" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>46111.002083333333</v>
       </c>
@@ -23066,7 +23065,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="182" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>46111.003472222219</v>
       </c>
@@ -23185,7 +23184,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="183" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>46111.079861111109</v>
       </c>
@@ -23304,7 +23303,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="184" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>46111.125694444447</v>
       </c>
@@ -23423,7 +23422,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="185" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>46111.167361111111</v>
       </c>
@@ -23542,7 +23541,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="186" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>46111.225694444453</v>
       </c>
@@ -23661,7 +23660,7 @@
         <v>1481963.3824154071</v>
       </c>
     </row>
-    <row r="187" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>46114.252083333333</v>
       </c>
@@ -23780,7 +23779,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="188" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>46115.309027777781</v>
       </c>
@@ -23899,7 +23898,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="189" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>46115.350694444453</v>
       </c>
@@ -24018,7 +24017,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="190" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>46115.376388888893</v>
       </c>
@@ -24137,7 +24136,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="191" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>46115.420138888891</v>
       </c>
@@ -24256,7 +24255,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="192" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>46115.461805555547</v>
       </c>
@@ -24375,7 +24374,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="193" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>46115.53125</v>
       </c>
@@ -24494,7 +24493,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="194" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>46115.543749999997</v>
       </c>
@@ -24613,7 +24612,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="195" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>46115.584722222222</v>
       </c>
@@ -24732,7 +24731,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="196" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>46115.629861111112</v>
       </c>
@@ -24851,7 +24850,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="197" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>46115.664583333331</v>
       </c>
@@ -24970,7 +24969,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="198" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>46115.70208333333</v>
       </c>
@@ -25089,7 +25088,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="199" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>46115.737500000003</v>
       </c>
@@ -25208,7 +25207,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="200" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>46115.773611111108</v>
       </c>
@@ -25327,7 +25326,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="201" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>46115.808333333327</v>
       </c>
@@ -25446,7 +25445,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="202" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>46115.86041666667</v>
       </c>
@@ -25565,7 +25564,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="203" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>46115.897222222222</v>
       </c>
@@ -25684,7 +25683,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="204" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>46115.972916666673</v>
       </c>
@@ -25803,7 +25802,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="205" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>46115.000694444447</v>
       </c>
@@ -25922,7 +25921,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="206" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>46115.047222222223</v>
       </c>
@@ -26041,7 +26040,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="207" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>46115.081250000003</v>
       </c>
@@ -26160,7 +26159,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="208" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>46115.085416666669</v>
       </c>
@@ -26279,7 +26278,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="209" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>46115.157638888893</v>
       </c>
@@ -26398,7 +26397,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="210" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>46115.198611111111</v>
       </c>
@@ -26517,7 +26516,7 @@
         <v>114000</v>
       </c>
     </row>
-    <row r="211" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>46115.249305555553</v>
       </c>
@@ -29611,7 +29610,7 @@
         <v>635687.57490943035</v>
       </c>
     </row>
-    <row r="237" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>46125.246527777781</v>
       </c>
@@ -29730,7 +29729,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="238" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>46126.295138888891</v>
       </c>
@@ -29849,7 +29848,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="239" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>46126.336805555547</v>
       </c>
@@ -29968,7 +29967,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="240" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>46126.392361111109</v>
       </c>
@@ -30087,7 +30086,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="241" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>46126.440972222219</v>
       </c>
@@ -30206,7 +30205,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="242" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>46126.461111111108</v>
       </c>
@@ -30325,7 +30324,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="243" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>46126.53125</v>
       </c>
@@ -30444,7 +30443,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="244" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>46126.545138888891</v>
       </c>
@@ -30563,7 +30562,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="245" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>46126.621527777781</v>
       </c>
@@ -30682,7 +30681,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="246" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>46126.663194444453</v>
       </c>
@@ -30801,7 +30800,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="247" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>46126.704861111109</v>
       </c>
@@ -30920,7 +30919,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="248" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>46126.746527777781</v>
       </c>
@@ -31039,7 +31038,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="249" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>46126.75277777778</v>
       </c>
@@ -31158,7 +31157,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="250" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>46126.822916666657</v>
       </c>
@@ -31277,7 +31276,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="251" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>46126.836805555547</v>
       </c>
@@ -31396,7 +31395,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="252" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>46126.899305555547</v>
       </c>
@@ -31515,7 +31514,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="253" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>46126.919444444437</v>
       </c>
@@ -31634,7 +31633,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="254" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>46126.989583333343</v>
       </c>
@@ -31753,7 +31752,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="255" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>46126.00277777778</v>
       </c>
@@ -31872,7 +31871,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="256" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>46126.066666666673</v>
       </c>
@@ -31991,7 +31990,7 @@
         <v>699889.76470566459</v>
       </c>
     </row>
-    <row r="257" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>46126.10833333333</v>
       </c>
@@ -35085,7 +35084,7 @@
         <v>859171.65545236133</v>
       </c>
     </row>
-    <row r="283" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>46132.246527777781</v>
       </c>
@@ -35204,7 +35203,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="284" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>46133.291666666657</v>
       </c>
@@ -35323,7 +35322,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="285" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>46133.333333333343</v>
       </c>
@@ -35442,7 +35441,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="286" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>46133.361805555563</v>
       </c>
@@ -35561,7 +35560,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="287" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>46133.415277777778</v>
       </c>
@@ -35680,7 +35679,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="288" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>46133.455555555563</v>
       </c>
@@ -35799,7 +35798,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="289" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>46133.46875</v>
       </c>
@@ -35918,7 +35917,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="290" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>46133.508333333331</v>
       </c>
@@ -36037,7 +36036,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="291" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>46133.559027777781</v>
       </c>
@@ -36156,7 +36155,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="292" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>46133.584722222222</v>
       </c>
@@ -36275,7 +36274,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="293" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>46133.626388888893</v>
       </c>
@@ -36394,7 +36393,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="294" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>46133.668055555558</v>
       </c>
@@ -36513,7 +36512,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="295" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>46133.709722222222</v>
       </c>
@@ -36632,7 +36631,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="296" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>46133.760416666657</v>
       </c>
@@ -36751,7 +36750,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="297" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>46133.802083333343</v>
       </c>
@@ -36870,7 +36869,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="298" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>46133.84375</v>
       </c>
@@ -36989,7 +36988,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="299" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>46133.875694444447</v>
       </c>
@@ -37108,7 +37107,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="300" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>46133.917361111111</v>
       </c>
@@ -37227,7 +37226,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="301" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>46133.959027777782</v>
       </c>
@@ -37346,7 +37345,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="302" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>46133.010416666657</v>
       </c>
@@ -37465,7 +37464,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="303" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>46133.052083333343</v>
       </c>
@@ -37584,7 +37583,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="304" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>46133.09375</v>
       </c>
@@ -37703,7 +37702,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="305" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>46133.126388888893</v>
       </c>
@@ -37822,7 +37821,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="306" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>46133.168055555558</v>
       </c>
@@ -37941,7 +37940,7 @@
         <v>1042618.706061644</v>
       </c>
     </row>
-    <row r="307" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>46133.210416666669</v>
       </c>
@@ -38060,7 +38059,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="308" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>46134.294444444437</v>
       </c>
@@ -38179,7 +38178,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="309" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>46134.362500000003</v>
       </c>
@@ -38298,7 +38297,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="310" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>46134.378472222219</v>
       </c>
@@ -38417,7 +38416,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="311" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>46134.42083333333</v>
       </c>
@@ -38536,7 +38535,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="312" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>46134.482638888891</v>
       </c>
@@ -38655,7 +38654,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="313" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>46134.513194444437</v>
       </c>
@@ -38774,7 +38773,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="314" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>46134.554861111108</v>
       </c>
@@ -38893,7 +38892,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="315" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>46134.591666666667</v>
       </c>
@@ -39012,7 +39011,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="316" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>46134.636805555558</v>
       </c>
@@ -39131,7 +39130,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="317" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>46134.675694444442</v>
       </c>
@@ -39250,7 +39249,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="318" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>46134.716666666667</v>
       </c>
@@ -39369,7 +39368,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="319" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>46134.760416666657</v>
       </c>
@@ -39488,7 +39487,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="320" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>46134.800694444442</v>
       </c>
@@ -39607,7 +39606,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="321" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>46134.842361111107</v>
       </c>
@@ -39726,7 +39725,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="322" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>46134.884027777778</v>
       </c>
@@ -39845,7 +39844,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="323" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>46134.925000000003</v>
       </c>
@@ -39964,7 +39963,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="324" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>46134.975694444453</v>
       </c>
@@ -40083,7 +40082,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="325" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>46134.017361111109</v>
       </c>
@@ -40202,7 +40201,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="326" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>46134.059027777781</v>
       </c>
@@ -40321,7 +40320,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="327" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>46134.100694444453</v>
       </c>
@@ -40440,7 +40439,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="328" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>46134.127083333333</v>
       </c>
@@ -40559,7 +40558,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="329" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>46134.197916666657</v>
       </c>
@@ -40678,7 +40677,7 @@
         <v>1085729.248230319</v>
       </c>
     </row>
-    <row r="330" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>46134.252083333333</v>
       </c>
@@ -40797,7 +40796,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="331" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>46135.342361111107</v>
       </c>
@@ -40916,7 +40915,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="332" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>46135.376388888893</v>
       </c>
@@ -41035,7 +41034,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="333" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>46135.416666666657</v>
       </c>
@@ -41154,7 +41153,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="334" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>46135.455555555563</v>
       </c>
@@ -41273,7 +41272,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="335" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>46135.49722222222</v>
       </c>
@@ -41392,7 +41391,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="336" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>46135.531944444447</v>
       </c>
@@ -41511,7 +41510,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="337" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>46135.572916666657</v>
       </c>
@@ -41630,7 +41629,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="338" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>46135.614583333343</v>
       </c>
@@ -41749,7 +41748,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="339" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>46135.65625</v>
       </c>
@@ -41868,7 +41867,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="340" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>46135.669444444437</v>
       </c>
@@ -41987,7 +41986,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="341" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>46135.693749999999</v>
       </c>
@@ -42106,7 +42105,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="342" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>46135.775000000001</v>
       </c>
@@ -42225,7 +42224,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="343" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>46135.814583333333</v>
       </c>
@@ -42344,7 +42343,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="344" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>46135.852777777778</v>
       </c>
@@ -42463,7 +42462,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="345" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>46135.897916666669</v>
       </c>
@@ -42582,7 +42581,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="346" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>46135.936111111107</v>
       </c>
@@ -42701,7 +42700,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="347" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>46135.960416666669</v>
       </c>
@@ -42820,7 +42819,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="348" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>46135.017361111109</v>
       </c>
@@ -42939,7 +42938,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="349" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>46135.045138888891</v>
       </c>
@@ -43058,7 +43057,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="350" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>46135.128472222219</v>
       </c>
@@ -43177,7 +43176,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="351" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>46135.170138888891</v>
       </c>
@@ -43296,7 +43295,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="352" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>46135.211805555547</v>
       </c>
@@ -43415,7 +43414,7 @@
         <v>1132027.242209319</v>
       </c>
     </row>
-    <row r="353" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>46135.253472222219</v>
       </c>
@@ -43534,7 +43533,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="354" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>46136.295138888891</v>
       </c>
@@ -43653,7 +43652,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="355" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>46136.333333333343</v>
       </c>
@@ -43772,7 +43771,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="356" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>46136.40625</v>
       </c>
@@ -43891,7 +43890,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="357" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>46136.418749999997</v>
       </c>
@@ -44010,7 +44009,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="358" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>46136.459722222222</v>
       </c>
@@ -44129,7 +44128,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="359" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>46136.501388888893</v>
       </c>
@@ -44248,7 +44247,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="360" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>46136.552083333343</v>
       </c>
@@ -44367,7 +44366,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="361" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>46136.584027777782</v>
       </c>
@@ -44486,7 +44485,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="362" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>46136.625694444447</v>
       </c>
@@ -44605,7 +44604,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="363" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>46136.666666666657</v>
       </c>
@@ -44724,7 +44723,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="364" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>46136.670138888891</v>
       </c>
@@ -44843,7 +44842,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="365" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>46136.746527777781</v>
       </c>
@@ -44962,7 +44961,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="366" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>46136.795138888891</v>
       </c>
@@ -45081,7 +45080,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="367" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>46136.84375</v>
       </c>
@@ -45200,7 +45199,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="368" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>46136.884722222218</v>
       </c>
@@ -45319,7 +45318,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="369" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>46136.931944444441</v>
       </c>
@@ -45438,7 +45437,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="370" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
         <v>46136.973611111112</v>
       </c>
@@ -45557,7 +45556,7 @@
         <v>1168338.401407093</v>
       </c>
     </row>
-    <row r="371" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>46137.274305555547</v>
       </c>
@@ -45676,7 +45675,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="372" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>46138.293055555558</v>
       </c>
@@ -45795,7 +45794,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="373" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>46138.34375</v>
       </c>
@@ -45914,7 +45913,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="374" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
         <v>46138.376388888893</v>
       </c>
@@ -46033,7 +46032,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="375" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>46138.427083333343</v>
       </c>
@@ -46152,7 +46151,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="376" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>46138.475694444453</v>
       </c>
@@ -46271,7 +46270,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="377" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>46138.517361111109</v>
       </c>
@@ -46390,7 +46389,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="378" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>46138.559027777781</v>
       </c>
@@ -46509,7 +46508,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="379" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>46138.600694444453</v>
       </c>
@@ -46628,7 +46627,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="380" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>46138.640972222223</v>
       </c>
@@ -46747,7 +46746,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="381" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>46138.682638888888</v>
       </c>
@@ -46866,7 +46865,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="382" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>46138.723611111112</v>
       </c>
@@ -46985,7 +46984,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="383" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>46138.751388888893</v>
       </c>
@@ -47104,7 +47103,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="384" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
         <v>46138.804861111108</v>
       </c>
@@ -47223,7 +47222,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="385" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
         <v>46138.845138888893</v>
       </c>
@@ -47342,7 +47341,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="386" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>46138.886111111111</v>
       </c>
@@ -47461,7 +47460,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="387" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>46138.927083333343</v>
       </c>
@@ -47580,7 +47579,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="388" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
         <v>46138.959722222222</v>
       </c>
@@ -47699,7 +47698,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="389" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
         <v>46138.003472222219</v>
       </c>
@@ -47818,7 +47817,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="390" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
         <v>46138.039583333331</v>
       </c>
@@ -47937,7 +47936,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="391" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A391" s="1">
         <v>46138.085416666669</v>
       </c>
@@ -48056,7 +48055,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="392" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A392" s="1">
         <v>46138.154861111107</v>
       </c>
@@ -48175,7 +48174,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="393" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A393" s="1">
         <v>46138.193055555559</v>
       </c>
@@ -48294,7 +48293,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="394" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A394" s="1">
         <v>46138.240972222222</v>
       </c>
@@ -48413,7 +48412,7 @@
         <v>1263300.5225654889</v>
       </c>
     </row>
-    <row r="395" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A395" s="1">
         <v>46138.277083333327</v>
       </c>
@@ -48532,7 +48531,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="396" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A396" s="1">
         <v>46139.294444444437</v>
       </c>
@@ -48651,7 +48650,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="397" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
         <v>46139.336111111108</v>
       </c>
@@ -48770,7 +48769,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="398" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A398" s="1">
         <v>46139.37777777778</v>
       </c>
@@ -48889,7 +48888,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="399" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>46139.447916666657</v>
       </c>
@@ -49008,7 +49007,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="400" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>46139.482638888891</v>
       </c>
@@ -49127,7 +49126,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="401" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>46139.524305555547</v>
       </c>
@@ -49246,7 +49245,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="402" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>46139.565972222219</v>
       </c>
@@ -49365,7 +49364,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="403" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>46139.585416666669</v>
       </c>
@@ -49484,7 +49483,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="404" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>46139.63958333333</v>
       </c>
@@ -49603,7 +49602,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="405" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>46139.668055555558</v>
       </c>
@@ -49722,7 +49721,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="406" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
         <v>46139.709722222222</v>
       </c>
@@ -49841,7 +49840,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="407" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A407" s="1">
         <v>46139.762499999997</v>
       </c>
@@ -49960,7 +49959,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="408" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A408" s="1">
         <v>46139.802777777782</v>
       </c>
@@ -50079,7 +50078,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="409" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>46139.84097222222</v>
       </c>
@@ -50198,7 +50197,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="410" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>46139.878472222219</v>
       </c>
@@ -50317,7 +50316,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="411" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>46139.916666666657</v>
       </c>
@@ -50436,7 +50435,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="412" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
         <v>46139.958333333343</v>
       </c>
@@ -50555,7 +50554,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="413" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A413" s="1">
         <v>46139.995833333327</v>
       </c>
@@ -50674,7 +50673,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="414" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A414" s="1">
         <v>46139.041666666657</v>
       </c>
@@ -50793,7 +50792,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="415" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A415" s="1">
         <v>46139.082638888889</v>
       </c>
@@ -50912,7 +50911,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="416" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A416" s="1">
         <v>46139.086805555547</v>
       </c>
@@ -51031,7 +51030,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="417" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A417" s="1">
         <v>46139.161111111112</v>
       </c>
@@ -51150,7 +51149,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="418" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>46139.170138888891</v>
       </c>
@@ -51269,7 +51268,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="419" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
         <v>46139.236805555563</v>
       </c>
@@ -51388,7 +51387,7 @@
         <v>1311361.6616897059</v>
       </c>
     </row>
-    <row r="420" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A420" s="1">
         <v>46141.246527777781</v>
       </c>
@@ -51507,7 +51506,7 @@
         <v>1408134.789949534</v>
       </c>
     </row>
-    <row r="421" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A421" s="1">
         <v>46142.432638888888</v>
       </c>
@@ -51626,7 +51625,7 @@
         <v>1408134.789949534</v>
       </c>
     </row>
-    <row r="422" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A422" s="1">
         <v>46142.46597222222</v>
       </c>
@@ -51745,7 +51744,7 @@
         <v>1408134.789949534</v>
       </c>
     </row>
-    <row r="423" spans="1:39" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A423" s="1">
         <v>46142.510416666657</v>
       </c>
@@ -54008,20 +54007,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AM441" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="19">
-      <filters>
-        <filter val="T 13.1.Recycle"/>
-        <filter val="T 13.5.1.Recycle"/>
-        <filter val="T 13.5.2.Recycle"/>
-        <filter val="T 14.2.Recycle"/>
-        <filter val="T 15.2.Recycle"/>
-        <filter val="T 15.5.2.Recycle"/>
-        <filter val="T 16.2.Recycle"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="30">
       <filters>
+        <filter val="13"/>
+        <filter val="13.5"/>
+        <filter val="14"/>
+        <filter val="15"/>
+        <filter val="15.5"/>
         <filter val="16"/>
+        <filter val="18"/>
       </filters>
     </filterColumn>
   </autoFilter>
